--- a/Datos_SSPP.xlsx
+++ b/Datos_SSPP.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF69"/>
+  <dimension ref="A1:AF103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7190,6 +7190,2687 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP.</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>6097424-9</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>06/11/2025 al 05/12/2025</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>678.86</v>
+      </c>
+      <c r="G70" t="n">
+        <v>15960</v>
+      </c>
+      <c r="O70" t="n">
+        <v>11042720</v>
+      </c>
+      <c r="P70" t="n">
+        <v>10834600</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>208120</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6097424-9_376749483-0.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>6454244-2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>06 NOV/2025 A 05 DIC/2025</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>747.3099999999999</v>
+      </c>
+      <c r="G71" t="n">
+        <v>11280</v>
+      </c>
+      <c r="O71" t="n">
+        <v>8501880</v>
+      </c>
+      <c r="P71" t="n">
+        <v>8429670</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>72210</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ajustes a la decena</t>
+        </is>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6454244-2_376753685-9.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>7377766-2</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>06/03/2025 al 03/04/2025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>858.4299999999999</v>
+      </c>
+      <c r="G72" t="n">
+        <v>15680</v>
+      </c>
+      <c r="O72" t="n">
+        <v>16837560</v>
+      </c>
+      <c r="P72" t="n">
+        <v>16771690</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>65870</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>REVISION EQUIPO DE MEDIDA, VALOR SELLOS</t>
+        </is>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Buró 25 T3</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_7377766-2_348535132-1.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>6097424-9</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>07/10/2025 al 05/11/2025</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>11/2025</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>694.54</v>
+      </c>
+      <c r="G73" t="n">
+        <v>15960</v>
+      </c>
+      <c r="O73" t="n">
+        <v>11286270</v>
+      </c>
+      <c r="P73" t="n">
+        <v>11084880</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>201390</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6097424-9_373250165-6.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>6454244-2</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>07/10/2025 al 05/11/2025</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>11/2025</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>767.79</v>
+      </c>
+      <c r="G74" t="n">
+        <v>11400</v>
+      </c>
+      <c r="O74" t="n">
+        <v>8820000</v>
+      </c>
+      <c r="P74" t="n">
+        <v>8752800</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>67200</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ajustes a la decena</t>
+        </is>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6454244-2_373248201-5.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7377766-2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>05 JUL/2025 al 31 JUL/2025</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>09/2025</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1055.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10509</v>
+      </c>
+      <c r="O75" t="n">
+        <v>7420280</v>
+      </c>
+      <c r="P75" t="n">
+        <v>7354790</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>65490</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>ABONO COMPONENTE TARIFARIO RES, Ajustes a la decena</t>
+        </is>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Buró 25 T3</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_7377766-2_364692222-2.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP.</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>7377766-2</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>06 JUN/2025 A 04 JUL/2025</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>836.28</v>
+      </c>
+      <c r="G76" t="n">
+        <v>14219</v>
+      </c>
+      <c r="O76" t="n">
+        <v>14340600</v>
+      </c>
+      <c r="P76" t="n">
+        <v>14269280</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>71320</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ajustes a la decena, Contribución comercial sencilla, ASEO - Reliquidación aprovecha</t>
+        </is>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Buró 25 T3</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_7377766-2_359184816-3.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A ESP</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>7377766-2</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>06/05/2025 al 05/06/2025</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>06/2025</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>799.42</v>
+      </c>
+      <c r="G77" t="n">
+        <v>15200</v>
+      </c>
+      <c r="O77" t="n">
+        <v>14647830</v>
+      </c>
+      <c r="P77" t="n">
+        <v>14581400</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>66430</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>CONTRIBUCION COMERCIAL SENCILL $2.430.233, Ajustes a la decena $4</t>
+        </is>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Buró 25 T3</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_7377766-2_355573020-4.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>7377766-2</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>04 ABR/2025 al 05 MAY/2025</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>05/2025</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>831.08</v>
+      </c>
+      <c r="G78" t="n">
+        <v>16160</v>
+      </c>
+      <c r="O78" t="n">
+        <v>16185490</v>
+      </c>
+      <c r="P78" t="n">
+        <v>16116270</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>69220</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>CONTRIBUCION COMERCIAL SENCILL ($2.686.045), Ajustes a la decena ($1)</t>
+        </is>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Buró 25 T3</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_7377766-2_352123175-2.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP.</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>7377766-2</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>05/02/2025 al 05/03/2025</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>843.71</v>
+      </c>
+      <c r="G79" t="n">
+        <v>15200</v>
+      </c>
+      <c r="O79" t="n">
+        <v>15454520</v>
+      </c>
+      <c r="P79" t="n">
+        <v>15389190</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>65330</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>CONTRIBUCION COMERCIAL SENCILL ($2.564.865), Ajustes a la decena ($-2)</t>
+        </is>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Buró 25 T3</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_7377766-2_345266237-8.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ENEL COLOMBIA S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>7377766-2</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>08/01/2025 al 04/02/2025</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>853.92</v>
+      </c>
+      <c r="G80" t="n">
+        <v>12960</v>
+      </c>
+      <c r="O80" t="n">
+        <v>13347080</v>
+      </c>
+      <c r="P80" t="n">
+        <v>13280200</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>66880</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Buró 25 T3</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_7377766-2_341834383-2.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A ESP</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7377766-2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>06 DIC/2024 al 07 ENE/2025</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>01/2025</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>877.36</v>
+      </c>
+      <c r="G81" t="n">
+        <v>17440</v>
+      </c>
+      <c r="O81" t="n">
+        <v>18423250</v>
+      </c>
+      <c r="P81" t="n">
+        <v>18361430</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>61820</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Contribución Comercial Sencill, Ajustes a la decena</t>
+        </is>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Buró 25 T3</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_7377766-2_338231675-8.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Enel Bogotá</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>6097424-9</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>04 SEP/2025 A 06 OCT/2025</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>700.91</v>
+      </c>
+      <c r="G82" t="n">
+        <v>18240</v>
+      </c>
+      <c r="O82" t="n">
+        <v>12402220</v>
+      </c>
+      <c r="P82" t="n">
+        <v>12193060</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>209160</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Compensación CREG SERV.015/18 ($-591.482)</t>
+        </is>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6097424-9_369568927-6.pdf</t>
+        </is>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>6454244-2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>04 SEP/2025 A 06 OCT/2025</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>760,57</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>11760</v>
+      </c>
+      <c r="O83" t="n">
+        <v>9017620</v>
+      </c>
+      <c r="P83" t="n">
+        <v>8944290</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>73330</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ajustes a la decena, ASEO - RELIQUIDACIÓN APROVECHA</t>
+        </is>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6454244-2_369563863-6.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Enel Bogotá</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>6454244-2</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>05/08/2025 al 03/09/2025</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>09/2025</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>745.59</v>
+      </c>
+      <c r="G84" t="n">
+        <v>9720</v>
+      </c>
+      <c r="O84" t="n">
+        <v>7313810</v>
+      </c>
+      <c r="P84" t="n">
+        <v>7247100</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>66710</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6454244-2_365943746-6.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>6097424-9</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>05/07/2025 al 04/08/2025</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>678.85</v>
+      </c>
+      <c r="G85" t="n">
+        <v>16720</v>
+      </c>
+      <c r="O85" t="n">
+        <v>11546640</v>
+      </c>
+      <c r="P85" t="n">
+        <v>11350310</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>196330</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6097424-9_362479969-0.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>6454244-2</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>05 JUL/2025 A 04 AGO/2025</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>733.14</v>
+      </c>
+      <c r="G86" t="n">
+        <v>11520</v>
+      </c>
+      <c r="O86" t="n">
+        <v>8511300</v>
+      </c>
+      <c r="P86" t="n">
+        <v>8445810</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>65490</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ajustes a la decena</t>
+        </is>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6454244-2_362481086-0.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>6097424-9</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>06/06/2025 al 04/07/2025</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>723.51</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>15200</v>
+      </c>
+      <c r="O87" t="n">
+        <v>11200260</v>
+      </c>
+      <c r="P87" t="n">
+        <v>10997390</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>202870</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ajustes a la decena, Reliquidación aprovecha</t>
+        </is>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6097424-9_359017693-7.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>6454244-2</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>06 JUN/2025 al 04 JUL/2025</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>783.58</v>
+      </c>
+      <c r="G88" t="n">
+        <v>10680</v>
+      </c>
+      <c r="O88" t="n">
+        <v>8439930</v>
+      </c>
+      <c r="P88" t="n">
+        <v>8368610</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>71320</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ajustes a la decena</t>
+        </is>
+      </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6454244-2_359021672-5.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>6097424-9</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>06 MAY/2025 A 05 JUN/2025</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>06/2025</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>690.1</v>
+      </c>
+      <c r="G89" t="n">
+        <v>16720</v>
+      </c>
+      <c r="O89" t="n">
+        <v>11715780</v>
+      </c>
+      <c r="P89" t="n">
+        <v>11538470</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>177310</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6097424-9_355572429-2.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>6454244-2</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>06 MAY/2025 al 05 JUN/2025</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>06/2025</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>746.15</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>11520</v>
+      </c>
+      <c r="O90" t="n">
+        <v>8662030</v>
+      </c>
+      <c r="P90" t="n">
+        <v>8595600</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>66430</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ajustes a la decena</t>
+        </is>
+      </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6454244-2_355562597-2.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP.</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>6097424-9</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>04 ABR/2025 A 05 MAY/2025</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>05/2025</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>720.48</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>21280</v>
+      </c>
+      <c r="O91" t="n">
+        <v>15510130</v>
+      </c>
+      <c r="P91" t="n">
+        <v>15331820</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>178310</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ajustes a la decena, Contribución no residencial aseo, Reliquidación aprovecha</t>
+        </is>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6097424-9_352109830-6.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A ESP.</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>6454244-2</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>04 ABR/2025 al 05 MAY/2025</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>05/2025</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>776,65</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>12840</v>
+      </c>
+      <c r="O92" t="n">
+        <v>10041440</v>
+      </c>
+      <c r="P92" t="n">
+        <v>9972230</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>69210</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6454244-2_352119721-1.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A ESP</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>6097424-9</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>06 MAR/2025 A 03 ABR/2025</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>750.65</v>
+      </c>
+      <c r="G93" t="n">
+        <v>19000</v>
+      </c>
+      <c r="O93" t="n">
+        <v>14438050</v>
+      </c>
+      <c r="P93" t="n">
+        <v>14262270</v>
+      </c>
+      <c r="R93" t="n">
+        <v>175780</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6097424-9_348529746-8.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ENEL COLOMBIA S.A ESP.</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>6454244-2</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>06 MAR/2025 A 03 ABR/2025</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>806.58</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>13200</v>
+      </c>
+      <c r="O94" t="n">
+        <v>10712710</v>
+      </c>
+      <c r="P94" t="n">
+        <v>10646840</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>65870</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V94" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6454244-2_348522954-3.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>6097424-9</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>05 FEB/2025 A 05 MAR/2025</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>736.56</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>18240</v>
+      </c>
+      <c r="O95" t="n">
+        <v>13609590</v>
+      </c>
+      <c r="P95" t="n">
+        <v>13434810</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>174780</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6097424-9_345082837-6.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A ESP.</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>6454244-2</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>05 FEB/2025 A 05 MAR/2025</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>797.29</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>13200</v>
+      </c>
+      <c r="O96" t="n">
+        <v>10589540</v>
+      </c>
+      <c r="P96" t="n">
+        <v>10524210</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>65330</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ajustes a la decena $2</t>
+        </is>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6454244-2_345093747-7.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP.</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>6097424-9</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>08 ENE/2025 A 04 FEB/2025</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>736.9299999999999</v>
+      </c>
+      <c r="G97" t="n">
+        <v>18240</v>
+      </c>
+      <c r="O97" t="n">
+        <v>13617530</v>
+      </c>
+      <c r="P97" t="n">
+        <v>13441580</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>175950</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6097424-9_341661078-8.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A ESP.</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>6454244-2</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>08 ENE/2025 A 04 FEB/2025</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>807.75</v>
+      </c>
+      <c r="G98" t="n">
+        <v>11520</v>
+      </c>
+      <c r="O98" t="n">
+        <v>9372160</v>
+      </c>
+      <c r="P98" t="n">
+        <v>9305280</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>66880</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V98" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6454244-2_341661697-3.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>6454244-2</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>06 DIC/2024 A 07 ENE/2025</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>01/2025</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>831.59</v>
+      </c>
+      <c r="G99" t="n">
+        <v>13920</v>
+      </c>
+      <c r="O99" t="n">
+        <v>11637580</v>
+      </c>
+      <c r="P99" t="n">
+        <v>11575760</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>61820</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ajustes a la decena ($4)</t>
+        </is>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Buró 25 T2</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_6454244-2_338225513-7.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>4269607-3</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>05 NOV/2025 A 04 DIC/2025</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>747.3099999999999</v>
+      </c>
+      <c r="G100" t="n">
+        <v>20160</v>
+      </c>
+      <c r="O100" t="n">
+        <v>18584450</v>
+      </c>
+      <c r="P100" t="n">
+        <v>18078950</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>505500</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>CONTRIBUCION COMERCIAL SENCILL</t>
+        </is>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Buró 26</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_4269607-3_376562839-2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>4269607-3</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>03/09/2025 al 03/10/2025</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>760.5700000000001</v>
+      </c>
+      <c r="G101" t="n">
+        <v>21360</v>
+      </c>
+      <c r="O101" t="n">
+        <v>20008220</v>
+      </c>
+      <c r="P101" t="n">
+        <v>19494900</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>513320</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Buró 26</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_4269607-3_369373013-6.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Enel Colombia S.A. ESP</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>4269607-3</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>04/10/2025 al 04/11/2025</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>11/2025</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>767.79</v>
+      </c>
+      <c r="G102" t="n">
+        <v>20400</v>
+      </c>
+      <c r="O102" t="n">
+        <v>19265860</v>
+      </c>
+      <c r="P102" t="n">
+        <v>18795480</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>470380</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>CONTRIBUCION COMERCIAL SENCILL ($3.132.580), Ajustes a la decena ($-2)</t>
+        </is>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Buró 26</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_4269607-3_373063673-7.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ENEL COLOMBIA S.A ESP.</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>4269607-3</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>04 JUL/2025 A 01 AGO/2025</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>733.14</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>18480.0</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>16716620.0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>16258190.0</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>458430.0</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Buró 26</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>Enel-Codensa_4269607-3_362292600-2.PDF</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
